--- a/aozora-quiz/questions-data.xlsx
+++ b/aozora-quiz/questions-data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +472,11 @@
           <t>URL</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>抜粋位置</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="80" customHeight="1">
       <c r="A2" t="n">
@@ -504,6 +510,11 @@
           <t>https://www.aozora.gr.jp/cards/000148/./files/773_14560.html</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="80" customHeight="1">
       <c r="A3" t="n">
@@ -511,20 +522,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>こころ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>夏目漱石</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>しかしおれの方から見てご覧、立場が少し違っているよ。つまり卒業はお前に取ってより、このおれに取って結構なんだ。解ったかい」
+　私は一言もなかった。詫まる以上に恐縮して俯向いていた。父は平気なうちに自分の死を覚悟していたものとみえる。しかも私の卒業する前に死ぬだろうと思い定めていたとみえる。その卒業が父の心にどのくらい響くかも考えずにいた私は全く愚かものであった。私は鞄の中から卒業証書を取り出して、それを大事そうに父と母に見せた。証書は何かに圧し潰されて、元の形を失っていた。父はそれを鄭寧に伸した。
+「こんなものは巻いたなり手に持って来るものだ」
+「中に心でも入れると好かったのに」と母も傍から注意した。
+　父はしばらくそれを眺めた後、起って床の間の所へ行って、誰の目にもすぐはいるような正面へ証書を置いた。いつもの私ならすぐ何とかいうはずであったが、その時の私はまるで平生と違っていた。父や母に対して少しも逆らう気が起らなかった。私はだまって父の為すがままに任せておいた。一旦癖のついた鳥の子紙の証書は、なかなか父の自由にならなかった。適当な位置に置かれるや否や、</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000148/./files/773_14560.html</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>坊っちゃん</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>夏目漱石</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>一
 　親譲りの無鉄砲で小供の時から損ばかりしている。小学校に居る時分学校の二階から飛び降りて一週間ほど腰を抜かした事がある。なぜそんな無闇をしたと聞く人があるかも知れぬ。別段深い理由でもない。新築の二階から首を出していたら、同級生の一人が冗談に、いくら威張っても、そこから飛び降りる事は出来まい。弱虫やーい。と囃したからである。小使に負ぶさって帰って来た時、おやじが大きな眼をして二階ぐらいから飛び降りて腰を抜かす奴があるかと云ったから、この次は抜かさずに飛んで見せますと答えた。
@@ -532,32 +582,73 @@
 　庭を東へ二十歩に行き尽すと、南上がりにいささかばかりの菜園があって、真中に栗の木が一本立っている。これは命より大事な栗だ。</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000148/./files/752_14964.html</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>坊っちゃん</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>夏目漱石</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>――ほかの人に無暗に渾名なんか、つけるのは人に恨まれるもとになるから、やたらに使っちゃいけない、もしつけたら、清だけに手紙で知らせろ。――田舎者は人がわるいそうだから、気をつけてひどい目に遭わないようにしろ。――気候だって東京より不順に極ってるから、寝冷をして風邪を引いてはいけない。坊っちゃんの手紙はあまり短過ぎて、容子がよくわからないから、この次にはせめてこの手紙の半分ぐらいの長さのを書いてくれ。――宿屋へ茶代を五円やるのはいいが、あとで困りゃしないか、田舎へ行って頼りになるはお金ばかりだから、なるべく倹約して、万一の時に差支えないようにしなくっちゃいけない。――お小遣がなくて困るかも知れないから、為替で十円あげる。――先だって坊っちゃんからもらった五十円を、坊っちゃんが、東京へ帰って、うちを持つ時の足しにと思って、郵便局へ預けておいたが、この十円を引いてもまだ四十円あるから大丈夫だ。――なるほど女と云うものは細かいものだ。
+　おれが椽鼻で清の手紙をひらつかせながら、考え込んでいると、しきりの襖をあけて、萩野のお婆さんが晩めしを持ってきた。まだ見てお出でるのかなもし。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000148/./files/752_14964.html</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>吾輩は猫である</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>夏目漱石</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>一
 　吾輩は猫である。名前はまだ無い。
@@ -565,32 +656,73 @@
 　この書生の掌の裏でしばらくはよい心持に坐っておったが、</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000148/./files/789_14547.html</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>吾輩は猫である</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>夏目漱石</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>今度は後方だと振りむく途端に、五寸近くある大な奴がひらりと歯磨の袋を落して椽の下へ馳け込む。逃がすものかと続いて飛び下りたらもう影も姿も見えぬ。鼠を捕るのは思ったよりむずかしい者である。吾輩は先天的鼠を捕る能力がないのか知らん。
+　吾輩が風呂場へ廻ると、敵は戸棚から馳け出し、戸棚を警戒すると流しから飛び上り、台所の真中に頑張っていると三方面共少々ずつ騒ぎ立てる。小癪と云おうか、卑怯と云おうかとうてい彼等は君子の敵でない。吾輩は十五六回はあちら、こちらと気を疲らし心を労らして奔走努力して見たがついに一度も成功しない。残念ではあるがかかる小人を敵にしてはいかなる東郷大将も施こすべき策がない。始めは勇気もあり敵愾心もあり悲壮と云う崇高な美感さえあったがついには面倒と馬鹿気ているのと眠いのと疲れたので台所の真中へ坐ったなり動かない事になった。しかし動かんでも八方睨みを極め込んでいれば敵は小人だから大した事は出来んのである。目ざす敵と思った奴が、存外けちな野郎だと、戦争が名誉だと云う感じが消えて悪くいと云う念だけ残る。悪くいと云う念を通り過すと張り合が抜けてぼーとする。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000148/./files/789_14547.html</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>三四郎</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>夏目漱石</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>一
 　うとうととして目がさめると女はいつのまにか、隣のじいさんと話を始めている。このじいさんはたしかに前の前の駅から乗ったいなか者である。発車まぎわに頓狂な声を出して駆け込んで来て、いきなり肌をぬいだと思ったら背中にお灸のあとがいっぱいあったので、三四郎の記憶に残っている。じいさんが汗をふいて、肌を入れて、女の隣に腰をかけたまでよく注意して見ていたくらいである。
@@ -599,32 +731,80 @@
 　ただ顔だちからいうと、この女のほうがよほど上等である。口に締まりがある。目がはっきりしている。</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000148/./files/794_14946.html</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>三四郎</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>夏目漱石</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>「先生、せっかく大久保へ越したが、またこっちの方へ出なければならないようになりそうです」
+「なぜ」
+「妹が学校へ行き帰りに、戸山の原を通るのがいやだと言いだしましてね。それにぼくが夜実験をやるものですから、おそくまで待っているのがさむしくっていけないんだそうです。もっとも今のうちは母がいるからかまいませんが、もう少しして、母が国へ帰ると、あとは下女だけになるものですからね。臆病者の二人ではとうていしんぼうしきれないのでしょう。――じつにやっかいだな」と冗談半分の嘆声をもらしたが、「どうです里見さん、あなたの所へでも食客に置いてくれませんか」と美禰子の顔を見た。
+「いつでも置いてあげますわ」
+「どっちです。宗八さんのほうをですか、よし子さんのほうをですか」と与次郎が口を出した。
+「どちらでも」
+　三四郎だけ黙っていた。広田先生は少しまじめになって、
+「そうして君はどうする気なんだ」
+「妹の始末さえつけば、当分下宿してもいいです。それでなければ、またどこかへ引っ越さなければならない。いっそ学校の寄宿舎へでも入れようかと思うんですがね。なにしろ子供だから、ぼくがしじゅう行けるか、</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000148/./files/794_14946.html</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>羅生門</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>芥川龍之介</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>ある日の暮方の事である。一人の下人が、羅生門の下で雨やみを待っていた。
 　広い門の下には、この男のほかに誰もいない。ただ、所々丹塗の剥げた、大きな円柱に、蟋蟀が一匹とまっている。羅生門が、朱雀大路にある以上は、この男のほかにも、雨やみをする市女笠や揉烏帽子が、もう二三人はありそうなものである。それが、この男のほかには誰もいない。
@@ -632,64 +812,154 @@
 　その代りまた鴉がどこからか、</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000879/./files/127_15260.html</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>羅生門</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>芥川龍之介</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>これは、その濁った、黄いろい光が、隅々に蜘蛛の巣をかけた天井裏に、揺れながら映ったので、すぐにそれと知れたのである。この雨の夜に、この羅生門の上で、火をともしているからは、どうせただの者ではない。
+　下人は、守宮のように足音をぬすんで、やっと急な梯子を、一番上の段まで這うようにして上りつめた。そうして体を出来るだけ、平にしながら、頸を出来るだけ、前へ出して、恐る恐る、楼の内を覗いて見た。
+　見ると、楼の内には、噂に聞いた通り、幾つかの死骸が、無造作に棄ててあるが、火の光の及ぶ範囲が、思ったより狭いので、数は幾つともわからない。ただ、おぼろげながら、知れるのは、その中に裸の死骸と、着物を着た死骸とがあるという事である。勿論、中には女も男もまじっているらしい。そうして、その死骸は皆、それが、かつて、生きていた人間だと云う事実さえ疑われるほど、土を捏ねて造った人形のように、口を開いたり手を延ばしたりして、ごろごろ床の上にころがっていた。しかも、肩とか胸とかの高くなっている部分に、ぼんやりした火の光をうけて、低くなっている部分の影を一層暗くしながら、永久に唖の如く黙っていた。
+　下人は、</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000879/./files/127_15260.html</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>鼻</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>芥川龍之介</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>禅智内供の鼻と云えば、池の尾で知らない者はない。長さは五六寸あって上唇の上から顋の下まで下っている。形は元も先も同じように太い。云わば細長い腸詰めのような物が、ぶらりと顔のまん中からぶら下っているのである。
 　五十歳を越えた内供は、沙弥の昔から、内道場供奉の職に陞った今日まで、内心では始終この鼻を苦に病んで来た。勿論表面では、今でもさほど気にならないような顔をしてすましている。これは専念に当来の浄土を渇仰すべき僧侶の身で、鼻の心配をするのが悪いと思ったからばかりではない。それよりむしろ、自分で鼻を気にしていると云う事を、人に知られるのが嫌だったからである。内供は日常の談話の中に、鼻と云う語が出て来るのを何よりも惧れていた。
 　内供が鼻を持てあました理由は二つある。――一つは実際的に、鼻の長いのが不便だったからである。第一飯を食う時にも独りでは食えない。独りで食えば、鼻の先が鋺の中の飯へとどいてしまう。そこで内供は弟子の一人を膳の向うへ坐らせて、飯を食う間中、広さ一寸長さ二尺ばかりの板で、鼻を持上げていて貰う事にした。しかしこうして飯を食うと云う事は、持上げている弟子にとっても、</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000879/./files/42_15228.html</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鼻</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>芥川龍之介</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>そこで折敷へ穴をあけて、それを提の蓋にして、その穴から鼻を湯の中へ入れる事にした。鼻だけはこの熱い湯の中へ浸しても、少しも熱くないのである。しばらくすると弟子の僧が云った。
+　――もう茹った時分でござろう。
+　内供は苦笑した。これだけ聞いたのでは、誰も鼻の話とは気がつかないだろうと思ったからである。鼻は熱湯に蒸されて、蚤の食ったようにむず痒い。
+　弟子の僧は、内供が折敷の穴から鼻をぬくと、そのまだ湯気の立っている鼻を、両足に力を入れながら、踏みはじめた。内供は横になって、鼻を床板の上へのばしながら、弟子の僧の足が上下に動くのを眼の前に見ているのである。弟子の僧は、時々気の毒そうな顔をして、内供の禿げ頭を見下しながら、こんな事を云った。
+　――痛うはござらぬかな。医師は責めて踏めと申したで。じゃが、痛うはござらぬかな。
+　内供は首を振って、痛くないと云う意味を示そうとした。所が鼻を踏まれているので思うように首が動かない。そこで、上眼を使って、弟子の僧の足に皹のきれているのを眺めながら、腹を立てたような声で、
+――痛うはないて。
+　と答えた。実際鼻はむず痒い所を踏まれるので、</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000879/./files/42_15228.html</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>蜘蛛の糸</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>芥川龍之介</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>一
 　ある日の事でございます。御釈迦様は極楽の蓮池のふちを、独りでぶらぶら御歩きになっていらっしゃいました。池の中に咲いている蓮の花は、みんな玉のようにまっ白で、そのまん中にある金色の蕊からは、何とも云えない好い匂が、絶間なくあたりへ溢れて居ります。極楽は丁度朝なのでございましょう。
@@ -697,32 +967,74 @@
 　するとその地獄の底に、陀多と云う男が一人、ほかの罪人と一しょに蠢いている姿が、御眼に止まりました。この陀多と云う男は、人を殺したり家に火をつけたり、いろいろ悪事を働いた大泥坊でございますが、それでもたった一つ、善い事を致した覚えがございます。と申しますのは、ある時この男が深い林の中を通りますと、小さな蜘蛛が一匹、路ばたを這って行くのが見えました。そこで陀多は早速足を挙げて、踏み殺そうと致しましたが、「いや、いや、</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000879/./files/92_14545.html</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蜘蛛の糸</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>芥川龍之介</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ところがある時の事でございます。何気なく陀多が頭を挙げて、血の池の空を眺めますと、そのひっそりとした暗の中を、遠い遠い天上から、銀色の蜘蛛の糸が、まるで人目にかかるのを恐れるように、一すじ細く光りながら、するすると自分の上へ垂れて参るのではございませんか。陀多はこれを見ると、思わず手を拍って喜びました。この糸に縋りついて、どこまでものぼって行けば、きっと地獄からぬけ出せるのに相違ございません。いや、うまく行くと、極楽へはいる事さえも出来ましょう。そうすれば、もう針の山へ追い上げられる事もなくなれば、血の池に沈められる事もある筈はございません。
+　こう思いましたから陀多は、早速その蜘蛛の糸を両手でしっかりとつかみながら、一生懸命に上へ上へとたぐりのぼり始めました。元より大泥坊の事でございますから、こう云う事には昔から、慣れ切っているのでございます。
+　しかし地獄と極楽との間は、何万里となくございますから、いくら焦って見た所で、容易に上へは出られません。ややしばらくのぼる中に、とうとう陀多もくたびれて、もう一たぐりも上の方へはのぼれなくなってしまいました。そこで仕方がございませんから、</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000879/./files/92_14545.html</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>藪の中</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>芥川龍之介</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>これは孝子伝吉の父の仇を打った話である。
 　伝吉は信州水内郡笹山村の百姓の一人息子である。伝吉の父は伝三と云い、「酒を好み、博奕を好み、喧嘩口論を好」んだと云うから、まず一村の人々にはならずもの扱いをされていたらしい。（註一）母は伝吉を産んだ翌年、病死してしまったと云うものもある。あるいはまた情夫の出来たために出奔してしまったと云うものもある。（註二）しかし事実はどちらにしろ、この話の始まる頃にはいなくなっていたのに違いない。
@@ -731,62 +1043,148 @@
 　なおまた伝吉の墓のある笹山村の慈照寺（浄土宗）は「孝子伝吉物語」と云う木版の小冊子を頒っている。</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000879/./files/34_15220.html</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>藪の中</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>芥川龍之介</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>伝吉は勿論落胆した。一時は「神ほとけも讐の上を守らせ給うか」とさえ歎息した。この上仇を返そうとすればまず旅に出なければならない。しかし当てもない旅に出るのは現在の伝吉には不可能である。伝吉は烈しい絶望の余り、だんだん遊蕩に染まり出した。「農家義人伝」はこの変化を「交を博徒に求む、蓋し讐の所在を知らんと欲する也」と説明している。これもまたあるいは一解釈かも知れない。
+　伝吉はたちまち枡屋を逐われ、唐丸の松と称された博徒松五郎の乾児になった。爾来ほとんど二十年ばかりは無頼の生活を送っていたらしい。（註五）「木の葉」はこの間に伝吉の枡屋の娘を誘拐したり、長窪の本陣何某へ強請に行ったりしたことを伝えている。これも他の諸書に載せてないのを見れば、軽々に真偽を決することは出来ない。現に「農家義人伝」は「伝吉、一郷の悪少と共に屡横逆を行えりと云う。妄誕弁ずるに足らざる也。伝吉は父讐を復せんとするの孝子、豈、這般の無状あらんや」と「木の葉」の記事を否定している。けれども伝吉はこの間も仇打ちの一念は忘れなかったのであろう。比較的伝吉に同情を持たない皆川蜩庵さえこう書いている。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000879/./files/34_15220.html</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>走れメロス</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>太宰治</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>メロスは激怒した。必ず、かの邪智暴虐の王を除かなければならぬと決意した。メロスには政治がわからぬ。メロスは、村の牧人である。笛を吹き、羊と遊んで暮して来た。けれども邪悪に対しては、人一倍に敏感であった。きょう未明メロスは村を出発し、野を越え山越え、十里はなれた此のシラクスの市にやって来た。メロスには父も、母も無い。女房も無い。十六の、内気な妹と二人暮しだ。この妹は、村の或る律気な一牧人を、近々、花婿として迎える事になっていた。結婚式も間近かなのである。メロスは、それゆえ、花嫁の衣裳やら祝宴の御馳走やらを買いに、はるばる市にやって来たのだ。先ず、その品々を買い集め、それから都の大路をぶらぶら歩いた。メロスには竹馬の友があった。セリヌンティウスである。今は此のシラクスの市で、石工をしている。その友を、これから訪ねてみるつもりなのだ。久しく逢わなかったのだから、訪ねて行くのが楽しみである。歩いているうちにメロスは、まちの様子を怪しく思った。ひっそりしている。もう既に日も落ちて、まちの暗いのは当りまえだが、けれども、なんだか、夜のせいばかりでは無く、市全体が、やけに寂しい。のんきなメロスも、</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000035/./files/1567_14913.html</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>走れメロス</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>太宰治</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>メロスほどの男にも、やはり未練の情というものは在る。今宵呆然、歓喜に酔っているらしい花嫁に近寄り、
+「おめでとう。私は疲れてしまったから、ちょっとご免こうむって眠りたい。眼が覚めたら、すぐに市に出かける。大切な用事があるのだ。私がいなくても、もうおまえには優しい亭主があるのだから、決して寂しい事は無い。おまえの兄の、一ばんきらいなものは、人を疑う事と、それから、嘘をつく事だ。おまえも、それは、知っているね。亭主との間に、どんな秘密でも作ってはならぬ。おまえに言いたいのは、それだけだ。おまえの兄は、たぶん偉い男なのだから、おまえもその誇りを持っていろ。」
+　花嫁は、夢見心地で首肯いた。メロスは、それから花婿の肩をたたいて、
+「仕度の無いのはお互さまさ。私の家にも、宝といっては、妹と羊だけだ。他には、何も無い。全部あげよう。もう一つ、メロスの弟になったことを誇ってくれ。」
+　花婿は揉み手して、てれていた。メロスは笑って村人たちにも会釈して、宴席から立ち去り、羊小屋にもぐり込んで、死んだように深く眠った。
+　眼が覚めたのは翌る日の薄明の頃である。メロスは跳ね起き、南無三、寝過したか、いや、</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000035/./files/1567_14913.html</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>銀河鉄道の夜</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>宮沢賢治</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">一　午後の授業
 「ではみなさんは、そういうふうに川だと言われたり、乳の流れたあとだと言われたりしていた、このぼんやりと白いものがほんとうは何かご承知ですか」先生は、黒板につるした大きな黒い星座の図の、上から下へ白くけぶった銀河帯のようなところを指しながら、みんなに問いをかけました。
@@ -797,98 +1195,84 @@
 </t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000081/./files/43737_19215.html</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>山月記</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>中島敦</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>銀河鉄道の夜</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>宮沢賢治</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>隴西の李徴は博学才穎、天宝の末年、若くして名を虎榜に連ね、ついで江南尉に補せられたが、性、狷介、自ら恃むところ頗る厚く、賤吏に甘んずるを潔しとしなかった。いくばくもなく官を退いた後は、故山、略に帰臥し、人と交を絶って、ひたすら詩作に耽った。下吏となって長く膝を俗悪な大官の前に屈するよりは、詩家としての名を死後百年に遺そうとしたのである。しかし、文名は容易に揚らず、生活は日を逐うて苦しくなる。李徴は漸く焦躁に駆られて来た。この頃からその容貌も峭刻となり、肉落ち骨秀で、眼光のみ徒らに炯々として、曾て進士に登第した頃の豊頬の美少年の俤は、何処に求めようもない。数年の後、貧窮に堪えず、妻子の衣食のために遂に節を屈して、再び東へ赴き、一地方官吏の職を奉ずることになった。一方、これは、己の詩業に半ば絶望したためでもある。曾ての同輩は既に遥か高位に進み、彼が昔、鈍物として歯牙にもかけなかったその連中の下命を拝さねばならぬことが、往年の儁才李徴の自尊心を如何に傷けたかは、想像に難くない。彼は怏々として楽しまず、狂悖の性は愈々抑え難くなった。一年の後、公用で旅に出、汝水のほとりに宿った時、遂に発狂した。</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000119/./files/624_14544.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="80" customHeight="1">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>富嶽百景</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>太宰治</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>一
-　あわただしく、玄関をあける音が聞えて、私はその音で、眼をさましましたが、それは泥酔の夫の、深夜の帰宅にきまっているのでございますから、そのまま黙って寝ていました。
-　夫は、隣の部屋に電気をつけ、はあっはあっ、とすさまじく荒い呼吸をしながら、机の引出しや本箱の引出しをあけて掻きまわし、何やら捜している様子でしたが、やがて、どたりと畳に腰をおろして坐ったような物音が聞えまして、あとはただ、はあっはあっという荒い呼吸ばかりで、何をしている事やら、私が寝たまま、
-「おかえりなさいまし。ごはんは、おすみですか？　お戸棚に、おむすびがございますけど」
-　と申しますと、
-「や、ありがとう」といつになく優しい返事をいたしまして、「坊やはどうです。熱は、まだありますか？」とたずねます。
-　これも珍らしい事でございました。坊やは、来年は四つになるのですが、栄養不足のせいか、または夫の酒毒のせいか、病毒のせいか、よその二つの子供よりも小さいくらいで、歩く足許さえおぼつかなく、言葉もウマウマとか、イヤイヤとかを言えるくらいが関の山で、脳が悪いのではないかとも思われ、</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000035/./files/2253_14908.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>「あなた方は、どちらへいらっしゃるんですか」
+「どこまでも行くんです」ジョバンニは、少しきまり悪そうに答えました。
+「それはいいね。この汽車は、じっさい、どこまででも行きますぜ」
+「あなたはどこへ行くんです」カムパネルラが、いきなり、喧嘩のようにたずねましたので、ジョバンニは思わずわらいました。すると、向こうの席にいた、とがった帽子をかぶり、大きな鍵を腰に下げた人も、ちらっとこっちを見てわらいましたので、カムパネルラも、つい顔を赤くして笑いだしてしまいました。ところがその人は別におこったでもなく、頬をぴくぴくしながら返事をしました。
+「わっしはすぐそこで降ります。わっしは、鳥をつかまえる商売でね」
+「何鳥ですか」
+「鶴や雁です。さぎも白鳥もです」
+「鶴はたくさんいますか」
+「いますとも、さっきから鳴いてまさあ。聞かなかったのですか」
+「いいえ」
+「いまでも聞こえるじゃありませんか。そら、耳をすまして聴いてごらんなさい」
+　二人は眼を挙げ、耳をすましました。ごとごと鳴る汽車のひびきと、すすきの風との間から、ころんころんと水の湧くような音が聞こえて来るのでした。
+「鶴、</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000081/./files/43737_19215.html</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>注文の多い料理店</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>宮沢賢治</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>二人の若い紳士が、すっかりイギリスの兵隊のかたちをして、ぴかぴかする鉄砲をかついで、白熊のような犬を二疋つれて、だいぶ山奥の、木の葉のかさかさしたとこを、こんなことを云いながら、あるいておりました。
 「ぜんたい、ここらの山は怪しからんね。鳥も獣も一疋も居やがらん。なんでも構わないから、早くタンタアーンと、やって見たいもんだなあ。」
@@ -900,192 +1284,87 @@
 　はじめの紳士は、すこし顔いろを悪くして、じっと、もひとりの紳士の、</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000081/./files/43754_17659.html</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="80" customHeight="1">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>高瀬舟</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>森鴎外</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>注文の多い料理店</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>宮沢賢治</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">越後の春日を経て今津へ出る道を、珍らしい旅人の一群れが歩いている。母は三十歳を踰えたばかりの女で、二人の子供を連れている。姉は十四、弟は十二である。それに四十ぐらいの女中が一人ついて、くたびれた同胞二人を、「もうじきにお宿にお着きなさいます」と言って励まして歩かせようとする。二人の中で、姉娘は足を引きずるようにして歩いているが、それでも気が勝っていて、疲れたのを母や弟に知らせまいとして、折り折り思い出したように弾力のある歩きつきをして見せる。近い道を物詣りにでも歩くのなら、ふさわしくも見えそうな一群れであるが、笠やら杖やらかいがいしい出立ちをしているのが、誰の目にも珍らしく、また気の毒に感ぜられるのである。
-　道は百姓家の断えたり続いたりする間を通っている。砂や小石は多いが、秋日和によく乾いて、しかも粘土がまじっているために、よく固まっていて、海のそばのように踝を埋めて人を悩ますことはない。
-　藁葺きの家が何軒も立ち並んだ一構えが柞の林に囲まれて、それに夕日がかっとさしているところに通りかかった。
-「まああの美しい紅葉をごらん」と、先に立っていた母が指さして子供に言った。
-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000129/./files/689_23257.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>舞姫</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>森鴎外</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>石炭をば早や積み果てつ。中等室の卓のほとりはいと靜にて、熾熱燈の光の晴れがましきも徒なり。今宵は夜毎にこゝに集ひ來る骨牌仲間も「ホテル」に宿りて、舟に殘れるは余一人のみなれば。
-　五年前の事なりしが、平生の望足りて、洋行の官命を蒙り、このセイゴンの港まで來し頃は、目に見るもの、耳に聞くもの、一つとして新ならぬはなく、筆に任せて書き記しつる紀行文日ごとに幾千言をかなしけむ、當時の新聞に載せられて、世の人にもてはやされしかど、今日になりておもへば、穉き思想、身の程知らぬ放言、さらぬも尋常の動植金石、さては風俗などをさへ珍しげにしるしゝを、心ある人はいかにか見けむ。こたびは途に上りしとき、日記ものせむとて買ひし册子もまだ白紙のまゝなるは、獨逸にて物學びせし間に、一種の「ニル、アドミラリイ」の氣象をや養ひ得たりけむ、あらず、これには別に故あり。
-　げに東に還る今の我は、西に航せし昔の我ならず、學問こそ猶心に飽き足らぬところも多かれ、浮世のうきふしをも知りたり、人の心の頼みがたきは言ふも更なり、われとわが心さへ變り易きをも悟り得たり。きのふの是はけふの非なるわが瞬間の感觸を、</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000129/./files/682_15414.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>檸檬</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>梶井基次郎</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>えたいの知れない不吉な塊が私の心を始終圧えつけていた。焦躁と言おうか、嫌悪と言おうか――酒を飲んだあとに宿酔があるように、酒を毎日飲んでいると宿酔に相当した時期がやって来る。それが来たのだ。これはちょっといけなかった。結果した肺尖カタルや神経衰弱がいけないのではない。また背を焼くような借金などがいけないのではない。いけないのはその不吉な塊だ。以前私を喜ばせたどんな美しい音楽も、どんな美しい詩の一節も辛抱がならなくなった。蓄音器を聴かせてもらいにわざわざ出かけて行っても、最初の二三小節で不意に立ち上がってしまいたくなる。何かが私を居堪らずさせるのだ。それで始終私は街から街を浮浪し続けていた。
-　何故だかその頃私は見すぼらしくて美しいものに強くひきつけられたのを覚えている。風景にしても壊れかかった街だとか、その街にしてもよそよそしい表通りよりもどこか親しみのある、汚い洗濯物が干してあったりがらくたが転がしてあったりむさくるしい部屋が覗いていたりする裏通りが好きであった。雨や風が蝕んでやがて土に帰ってしまう、と言ったような趣きのある街で、</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000074/./files/424_19826.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>桜の樹の下には</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>梶井基次郎</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>一
-　吉田は肺が悪い。寒になって少し寒い日が来たと思ったら、すぐその翌日から高い熱を出してひどい咳になってしまった。胸の臓器を全部押し上げて出してしまおうとしているかのような咳をする。四五日経つともうすっかり痩せてしまった。咳もあまりしない。しかしこれは咳が癒ったのではなくて、咳をするための腹の筋肉がすっかり疲れ切ってしまったからで、彼らが咳をするのを肯じなくなってしまったかららしい。それにもう一つは心臓がひどく弱ってしまって、一度咳をしてそれを乱してしまうと、それを再び鎮めるまでに非常に苦しい目を見なければならない。つまり咳をしなくなったというのは、身体が衰弱してはじめてのときのような元気がなくなってしまったからで、それが証拠には今度はだんだん呼吸困難の度を増して浅薄な呼吸を数多くしなければならなくなって来た。
-　病勢がこんなになるまでの間、吉田はこれを人並みの流行性感冒のように思って、またしても「明朝はもう少しよくなっているかもしれない」と思ってはその期待に裏切られたり、今日こそは医者を頼もうかと思ってはむだに辛抱をしたり、いつまでもひどい息切れを冒しては便所へ通ったり、</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000074/./files/425_19812.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>山椒大夫</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>森鴎外</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>わたくしの近頃書いた、歴史上の人物を取り扱つた作品は、小説だとか、小説でないとか云つて、友人間にも議論がある。しかし所謂 normativ な美学を奉じて、小説はかうなくてはならぬと云ふ学者の少くなつた時代には、此判断はなか／＼むづかしい。わたくし自身も、これまで書いた中で、材料を観照的に看た程度に、大分の相違のあるのを知つてゐる。中にも「栗山大膳」は、わたくしのすぐれなかつた健康と忙しかつた境界とのために、殆ど単に筋書をしたのみの物になつてゐる。そこでそれを太陽の某記者にわたす時、小説欄に入れずに、雑録様のものに交ぜて出して貰ひたいと云つた。某はそれを承諾した。さてそれが例になくわたくしの校正を経ずに、太陽に出たのを見れば、総ルビを振つて、小説欄に入れてある。殊に其ルビは数人で手分をして振つたものと見えて、二三ペエジ毎に変つてゐる。鉄砲頭が鉄砲のかみになつたり、左右良の城がさうらの城になつたりした処のあるのも、是非がない。
-　さうした行違のある栗山大膳は除くとしても、わたくしの前に言つた類の作品は、誰の小説とも違ふ。これは小説には、事実を自由に取捨して、</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://www.aozora.gr.jp/cards/000129/./files/684_18395.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>するとその裏側に、
+「注文はずいぶん多いでしょうがどうか一々こらえて下さい。」
+「これはぜんたいどういうんだ。」ひとりの紳士は顔をしかめました。
+「うん、これはきっと注文があまり多くて支度が手間取るけれどもごめん下さいと斯ういうことだ。」
+「そうだろう。早くどこか室の中にはいりたいもんだな。」
+「そしてテーブルに座りたいもんだな。」
+　ところがどうもうるさいことは、また扉が一つありました。そしてそのわきに鏡がかかって、その下には長い柄のついたブラシが置いてあったのです。
+　扉には赤い字で、
+「お客さまがた、ここで髪をきちんとして、それからはきもの
+　の泥を落してください。」
+と書いてありました。
+「これはどうも尤もだ。僕もさっき玄関で、山のなかだとおもって見くびったんだよ」
+「作法の厳しい家だ。きっとよほど偉い人たちが、たびたび来るんだ。」
+　そこで二人は、きれいに髪をけずって、靴の泥を落しました。
+　そしたら、どうです。ブラシを板の上に置くや否や、そいつがぼうっとかすんで無くなって、風がどうっと室の中に入ってきました。
+　二人はびっくりして、互によりそって、</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000081/./files/43754_17659.html</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>風の又三郎</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>宮沢賢治</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>雪婆んごは、遠くへ出かけて居りました。
 　猫のような耳をもち、ぼやぼやした灰いろの髪をした雪婆んごは、西の山脈の、ちぢれたぎらぎらの雲を越えて、遠くへでかけていたのです。
@@ -1096,63 +1375,668 @@
 　二疋の雪狼が、べろべろまっ赤な舌を吐きながら、象の頭のかたちをした、雪丘の上の方をあるいていました。こいつらは人の眼には見えないのですが、</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000081/./files/43757_17903.html</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="80" customHeight="1">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>風の又三郎</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>宮沢賢治</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>」
+「ええ、そうです。さあ、死んでしまえ。」雪童子はわざとひどくぶっつかりながらまたそっと云いました。
+「倒れているんだよ。動いちゃいけない。動いちゃいけないったら。」
+　狼どもが気ちがいのようにかけめぐり、黒い足は雪雲の間からちらちらしました。
+「そうそう、それでいいよ。さあ、降らしておくれ。なまけちゃ承知しないよ。ひゅうひゅうひゅう、ひゅひゅう。」雪婆んごは、また向うへ飛んで行きました。
+　子供はまた起きあがろうとしました。雪童子は笑いながら、も一度ひどくつきあたりました。もうそのころは、ぼんやり暗くなって、まだ三時にもならないに、日が暮れるように思われたのです。こどもは力もつきて、もう起きあがろうとしませんでした。雪童子は笑いながら、手をのばして、その赤い毛布を上からすっかりかけてやりました。
+「そうして睡っておいで。布団をたくさんかけてあげるから。そうすれば凍えないんだよ。あしたの朝までカリメラの夢を見ておいで。」
+　雪わらすは同じとこを何べんもかけて、雪をたくさんこどもの上にかぶせました。まもなく赤い毛布も見えなくなり、あたりとの高さも同じになってしまいました。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000081/./files/43757_17903.html</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>山月記</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中島敦</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>隴西の李徴は博学才穎、天宝の末年、若くして名を虎榜に連ね、ついで江南尉に補せられたが、性、狷介、自ら恃むところ頗る厚く、賤吏に甘んずるを潔しとしなかった。いくばくもなく官を退いた後は、故山、略に帰臥し、人と交を絶って、ひたすら詩作に耽った。下吏となって長く膝を俗悪な大官の前に屈するよりは、詩家としての名を死後百年に遺そうとしたのである。しかし、文名は容易に揚らず、生活は日を逐うて苦しくなる。李徴は漸く焦躁に駆られて来た。この頃からその容貌も峭刻となり、肉落ち骨秀で、眼光のみ徒らに炯々として、曾て進士に登第した頃の豊頬の美少年の俤は、何処に求めようもない。数年の後、貧窮に堪えず、妻子の衣食のために遂に節を屈して、再び東へ赴き、一地方官吏の職を奉ずることになった。一方、これは、己の詩業に半ば絶望したためでもある。曾ての同輩は既に遥か高位に進み、彼が昔、鈍物として歯牙にもかけなかったその連中の下命を拝さねばならぬことが、往年の儁才李徴の自尊心を如何に傷けたかは、想像に難くない。彼は怏々として楽しまず、狂悖の性は愈々抑え難くなった。一年の後、公用で旅に出、汝水のほとりに宿った時、遂に発狂した。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000119/./files/624_14544.html</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>山月記</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中島敦</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>この気持は誰にも分らない。誰にも分らない。己と同じ身の上に成った者でなければ。ところで、そうだ。己がすっかり人間でなくなって了う前に、一つ頼んで置きたいことがある。
+　袁はじめ一行は、息をのんで、叢中の声の語る不思議に聞入っていた。声は続けて言う。
+　他でもない。自分は元来詩人として名を成す積りでいた。しかも、業未だ成らざるに、この運命に立至った。曾て作るところの詩数百篇、固より、まだ世に行われておらぬ。遺稿の所在も最早判らなくなっていよう。ところで、その中、今も尚記誦せるものが数十ある。これを我が為に伝録して戴きたいのだ。何も、これに仍って一人前の詩人面をしたいのではない。作の巧拙は知らず、とにかく、産を破り心を狂わせてまで自分が生涯それに執着したところのものを、一部なりとも後代に伝えないでは、死んでも死に切れないのだ。
+　袁は部下に命じ、筆を執って叢中の声に随って書きとらせた。李徴の声は叢の中から朗々と響いた。長短凡そ三十篇、格調高雅、意趣卓逸、一読して作者の才の非凡を思わせるものばかりである。しかし、袁は感嘆しながらも漠然と次のように感じていた。成程、</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000119/./files/624_14544.html</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>富嶽百景</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>太宰治</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>一
+　あわただしく、玄関をあける音が聞えて、私はその音で、眼をさましましたが、それは泥酔の夫の、深夜の帰宅にきまっているのでございますから、そのまま黙って寝ていました。
+　夫は、隣の部屋に電気をつけ、はあっはあっ、とすさまじく荒い呼吸をしながら、机の引出しや本箱の引出しをあけて掻きまわし、何やら捜している様子でしたが、やがて、どたりと畳に腰をおろして坐ったような物音が聞えまして、あとはただ、はあっはあっという荒い呼吸ばかりで、何をしている事やら、私が寝たまま、
+「おかえりなさいまし。ごはんは、おすみですか？　お戸棚に、おむすびがございますけど」
+　と申しますと、
+「や、ありがとう」といつになく優しい返事をいたしまして、「坊やはどうです。熱は、まだありますか？」とたずねます。
+　これも珍らしい事でございました。坊やは、来年は四つになるのですが、栄養不足のせいか、または夫の酒毒のせいか、病毒のせいか、よその二つの子供よりも小さいくらいで、歩く足許さえおぼつかなく、言葉もウマウマとか、イヤイヤとかを言えるくらいが関の山で、脳が悪いのではないかとも思われ、</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000035/./files/2253_14908.html</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>富嶽百景</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>太宰治</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>やっぱりこれは、その、いまはやりの言葉で言えば奴隷根性というものなんでしょうね。私なんぞは、男の、それも、すれっからしと来ているのでございますから、たかが華族の、いや、奥さんの前ですけれども、四国の殿様のそのまた分家の、おまけに次男なんて、そんなのは何も私たちと身分のちがいがあろう筈が無いと思っていますし、まさかそんな、あさましく、くわっとなったりなどはしやしません。ですけれども、やはり、何だかどうもあの先生は、私にとっても苦手でして、もうこんどこそ、どんなにたのまれてもお酒は飲ませまいと固く決心していても、追われて来た人のように、意外の時刻にひょいとあらわれ、私どもの家へ来てやっとほっとしたような様子をするのを見ると、つい決心もにぶってお酒を出してしまうのです。酔っても、別に馬鹿騒ぎをするわけじゃないし、あれでお勘定さえきちんとしてくれたら、いいお客なんですがねえ。自分で自分の身分を吹聴するわけでもないし、天才だのなんだのとそんな馬鹿げた自慢をした事もありませんし、秋ちゃんなんかが、あの先生の傍で、私どもに、あの人の偉さに就いて広告したりなどすると、僕はお金がほしいんだ、</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000035/./files/2253_14908.html</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>高瀬舟</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>森鴎外</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">越後の春日を経て今津へ出る道を、珍らしい旅人の一群れが歩いている。母は三十歳を踰えたばかりの女で、二人の子供を連れている。姉は十四、弟は十二である。それに四十ぐらいの女中が一人ついて、くたびれた同胞二人を、「もうじきにお宿にお着きなさいます」と言って励まして歩かせようとする。二人の中で、姉娘は足を引きずるようにして歩いているが、それでも気が勝っていて、疲れたのを母や弟に知らせまいとして、折り折り思い出したように弾力のある歩きつきをして見せる。近い道を物詣りにでも歩くのなら、ふさわしくも見えそうな一群れであるが、笠やら杖やらかいがいしい出立ちをしているのが、誰の目にも珍らしく、また気の毒に感ぜられるのである。
+　道は百姓家の断えたり続いたりする間を通っている。砂や小石は多いが、秋日和によく乾いて、しかも粘土がまじっているために、よく固まっていて、海のそばのように踝を埋めて人を悩ますことはない。
+　藁葺きの家が何軒も立ち並んだ一構えが柞の林に囲まれて、それに夕日がかっとさしているところに通りかかった。
+「まああの美しい紅葉をごらん」と、先に立っていた母が指さして子供に言った。
+</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000129/./files/689_23257.html</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>高瀬舟</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>森鴎外</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>炉の向い側には茵三枚を畳ねて敷いて、山椒大夫がすわっている。大夫の赤顔が、座の右左に焚いてある炬火を照り反して、燃えるようである。三郎は炭火の中から、赤く焼けている火を抜き出す。それを手に持って、しばらく見ている。初め透き通るように赤くなっていた鉄が、次第に黒ずんで来る。そこで三郎は安寿を引き寄せて、火を顔に当てようとする。厨子王はその肘にからみつく。三郎はそれを蹴倒して右の膝に敷く。とうとう火を安寿の額に十文字に当てる。安寿の悲鳴が一座の沈黙を破って響き渡る。三郎は安寿を衝き放して、膝の下の厨子王を引き起し、その額にも火を十文字に当てる。新たに響く厨子王の泣き声が、ややかすかになった姉の声に交じる。三郎は火を棄てて、初め二人をこの広間へ連れて来たときのように、また二人の手をつかまえる。そして一座を見渡したのち、広い母屋を廻って、二人を三段の階の所まで引き出し、凍った土の上に衝き落す。二人の子供は創の痛みと心の恐れとに気を失いそうになるのを、ようよう堪え忍んで、どこをどう歩いたともなく、三の木戸の小家に帰る。臥所の上に倒れた二人は、しばらく死骸のように動かずにいたが、</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000129/./files/689_23257.html</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>舞姫</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>森鴎外</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>石炭をば早や積み果てつ。中等室の卓のほとりはいと靜にて、熾熱燈の光の晴れがましきも徒なり。今宵は夜毎にこゝに集ひ來る骨牌仲間も「ホテル」に宿りて、舟に殘れるは余一人のみなれば。
+　五年前の事なりしが、平生の望足りて、洋行の官命を蒙り、このセイゴンの港まで來し頃は、目に見るもの、耳に聞くもの、一つとして新ならぬはなく、筆に任せて書き記しつる紀行文日ごとに幾千言をかなしけむ、當時の新聞に載せられて、世の人にもてはやされしかど、今日になりておもへば、穉き思想、身の程知らぬ放言、さらぬも尋常の動植金石、さては風俗などをさへ珍しげにしるしゝを、心ある人はいかにか見けむ。こたびは途に上りしとき、日記ものせむとて買ひし册子もまだ白紙のまゝなるは、獨逸にて物學びせし間に、一種の「ニル、アドミラリイ」の氣象をや養ひ得たりけむ、あらず、これには別に故あり。
+　げに東に還る今の我は、西に航せし昔の我ならず、學問こそ猶心に飽き足らぬところも多かれ、浮世のうきふしをも知りたり、人の心の頼みがたきは言ふも更なり、われとわが心さへ變り易きをも悟り得たり。きのふの是はけふの非なるわが瞬間の感觸を、</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000129/./files/682_15414.html</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>舞姫</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>森鴎外</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>余は手袋をはめ、少し汚れたる外套を背に被ひて手をば通さず帽を取りてエリスに接吻して樓を下りつ。彼は凍れるを明け、亂れし髮を朔風に吹かせて余が乘りし車を見送りぬ。
+　余が車を下りしは「カイゼルホオフ」の入口なり。門者に祕書官相澤が室の番號を問ひて、久しく踏み慣れぬ大理石の階を登り、中央の柱に「プリユツシユ」を被へる「ゾフア」を据ゑつけ、正面には鏡を立てたる前房に入りぬ。外套をばこゝにて脱ぎ、廊をつたひて室の前まで往きしが、余は少し踟したり。同じく大學に在りし日に、余が品行の方正なるを激賞したる相澤が、けふは怎なる面もちして出迎ふらん。室に入りて相對して見れば、形こそ舊に比ぶれば肥えて逞ましくなりたれ、依然たる快活の氣象、我失行をもさまで意に介せざりきと見ゆ。別後の情を細叙するにも遑あらず、引かれて大臣に謁し、委托せられしは獨逸語にて記せる文書の急を要するを飜譯せよとの事なり。余が文書を受領して大臣の室を出でし時、相澤は跡より來て余と午餐を共にせんといひぬ。
+　食卓にては彼多く問ひて、我多く答へき。彼が生路は概ね平滑なりしに、轗軻數奇なるは我身の上なりければなり。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000129/./files/682_15414.html</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>檸檬</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>梶井基次郎</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>えたいの知れない不吉な塊が私の心を始終圧えつけていた。焦躁と言おうか、嫌悪と言おうか――酒を飲んだあとに宿酔があるように、酒を毎日飲んでいると宿酔に相当した時期がやって来る。それが来たのだ。これはちょっといけなかった。結果した肺尖カタルや神経衰弱がいけないのではない。また背を焼くような借金などがいけないのではない。いけないのはその不吉な塊だ。以前私を喜ばせたどんな美しい音楽も、どんな美しい詩の一節も辛抱がならなくなった。蓄音器を聴かせてもらいにわざわざ出かけて行っても、最初の二三小節で不意に立ち上がってしまいたくなる。何かが私を居堪らずさせるのだ。それで始終私は街から街を浮浪し続けていた。
+　何故だかその頃私は見すぼらしくて美しいものに強くひきつけられたのを覚えている。風景にしても壊れかかった街だとか、その街にしてもよそよそしい表通りよりもどこか親しみのある、汚い洗濯物が干してあったりがらくたが転がしてあったりむさくるしい部屋が覗いていたりする裏通りが好きであった。雨や風が蝕んでやがて土に帰ってしまう、と言ったような趣きのある街で、</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000074/./files/424_19826.html</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>檸檬</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>梶井基次郎</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>その日私はいつになくその店で買物をした。というのはその店には珍しい檸檬が出ていたのだ。檸檬などごくありふれている。がその店というのも見すぼらしくはないまでもただあたりまえの八百屋に過ぎなかったので、それまであまり見かけたことはなかった。いったい私はあの檸檬が好きだ。レモンエロウの絵具をチューブから搾り出して固めたようなあの単純な色も、それからあの丈の詰まった紡錘形の恰好も。――結局私はそれを一つだけ買うことにした。それからの私はどこへどう歩いたのだろう。私は長い間街を歩いていた。始終私の心を圧えつけていた不吉な塊がそれを握った瞬間からいくらか弛んで来たとみえて、私は街の上で非常に幸福であった。あんなに執拗かった憂鬱が、そんなものの一顆で紛らされる――あるいは不審なことが、逆説的なほんとうであった。それにしても心というやつはなんという不可思議なやつだろう。
+　その檸檬の冷たさはたとえようもなくよかった。その頃私は肺尖を悪くしていていつも身体に熱が出た。事実友達の誰彼に私の熱を見せびらかすために手の握り合いなどをしてみるのだが、私の掌が誰のよりも熱かった。その熱い故だったのだろう、</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000074/./files/424_19826.html</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>桜の樹の下には</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>梶井基次郎</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>一
+　吉田は肺が悪い。寒になって少し寒い日が来たと思ったら、すぐその翌日から高い熱を出してひどい咳になってしまった。胸の臓器を全部押し上げて出してしまおうとしているかのような咳をする。四五日経つともうすっかり痩せてしまった。咳もあまりしない。しかしこれは咳が癒ったのではなくて、咳をするための腹の筋肉がすっかり疲れ切ってしまったからで、彼らが咳をするのを肯じなくなってしまったかららしい。それにもう一つは心臓がひどく弱ってしまって、一度咳をしてそれを乱してしまうと、それを再び鎮めるまでに非常に苦しい目を見なければならない。つまり咳をしなくなったというのは、身体が衰弱してはじめてのときのような元気がなくなってしまったからで、それが証拠には今度はだんだん呼吸困難の度を増して浅薄な呼吸を数多くしなければならなくなって来た。
+　病勢がこんなになるまでの間、吉田はこれを人並みの流行性感冒のように思って、またしても「明朝はもう少しよくなっているかもしれない」と思ってはその期待に裏切られたり、今日こそは医者を頼もうかと思ってはむだに辛抱をしたり、いつまでもひどい息切れを冒しては便所へ通ったり、</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000074/./files/425_19812.html</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>桜の樹の下には</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>梶井基次郎</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>吉田の弟の店のあるところはその間でも比較的早くからできていた通り筋で両側はそんな町らしい、いろんなものを商う店が立ち並んでいた。
+　吉田は東京から病気が悪くなってその家へ帰って来たのが二年あまり前であった。吉田の帰って来た翌年吉田の父はその家で死んで、しばらくして吉田の弟も兵隊に行っていたのから帰って来ていよいよ落ち着いて商売をやっていくことになり嫁をもらった。そしてそれを機会にひとまず吉田も吉田の母も弟も、それまで外で家を持っていた吉田の兄の家の世話になることになり、その兄がそれまで住んでいた町から少し離れた田舎に、病人を住ますに都合のいい離れ家のあるいい家が見つかったのでそこへ引っ越したのがまだ三ヶ月ほど前であった。
+　吉田の弟は病室で母親を相手にしばらく当り触りのない自分の家の話などをしていたがやがて帰って行った。しばらくしてそれを送って行った母が部屋へ帰って来て、またしばらくしてのあとで、母は突然、
+「あの荒物屋の娘が死んだと」
+　と言って吉田に話しかけた。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000074/./files/425_19812.html</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>山椒大夫</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>森鴎外</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>わたくしの近頃書いた、歴史上の人物を取り扱つた作品は、小説だとか、小説でないとか云つて、友人間にも議論がある。しかし所謂 normativ な美学を奉じて、小説はかうなくてはならぬと云ふ学者の少くなつた時代には、此判断はなか／＼むづかしい。わたくし自身も、これまで書いた中で、材料を観照的に看た程度に、大分の相違のあるのを知つてゐる。中にも「栗山大膳」は、わたくしのすぐれなかつた健康と忙しかつた境界とのために、殆ど単に筋書をしたのみの物になつてゐる。そこでそれを太陽の某記者にわたす時、小説欄に入れずに、雑録様のものに交ぜて出して貰ひたいと云つた。某はそれを承諾した。さてそれが例になくわたくしの校正を経ずに、太陽に出たのを見れば、総ルビを振つて、小説欄に入れてある。殊に其ルビは数人で手分をして振つたものと見えて、二三ペエジ毎に変つてゐる。鉄砲頭が鉄砲のかみになつたり、左右良の城がさうらの城になつたりした処のあるのも、是非がない。
+　さうした行違のある栗山大膳は除くとしても、わたくしの前に言つた類の作品は、誰の小説とも違ふ。これは小説には、事実を自由に取捨して、</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000129/./files/684_18395.html</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>山椒大夫</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>森鴎外</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>妻は二人の子を連れて、岩代の信夫郡にゐた。二人の子は姉をあんじゆと云ひ、弟をつし王と云ふ。母は二人の育つのを待つて、父を尋ねに旅立つた。越後の直江の浦に来て、応化の橋の下に寝てゐると、そこへ山岡大夫と云ふ人買が来て、だまして舟に載せた。母子三人に、うば竹と云ふ老女が附いてゐたのである。さて沖に漕ぎ出して、山岡大夫は母子主従を二人の船頭に分けて売つた。一人は佐渡の二郎で母とうば竹とを買つて佐渡へ往く。一人は宮崎の三郎で、あんじゆとつし王とを買つて丹後の由良へ往く。佐渡へ渡つた母は、舟で入水したうば竹に離れて、粟の鳥を逐はせられる。由良に着いたあんじゆ、つし王は山椒大夫と云ふものに買はれて、姉は汐を汲ませられ、弟は柴を苅らせられる。子供等は親を慕つて逃げようとして、額に烙印をせられる。姉が弟を逃がして、跡に残つて責め殺される。弟は中山国分寺の僧に救はれて、京都に往く。清水寺で、つし王は梅津院と云ふ貴人に逢ふ。梅津院は七十を越して子がないので、子を授けて貰ひたさに参籠したのである。
+　つし王は梅津院の養子にせられて、陸奥守兼丹後守になる。つし王は佐渡へ渡つて母を連れ戻し、</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000129/./files/684_18395.html</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>堕落論</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>坂口安吾</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>半年のうちに世相は変った。醜の御楯といでたつ我は。大君のへにこそ死なめかへりみはせじ。若者達は花と散ったが、同じ彼等が生き残って闇屋となる。ももとせの命ねがはじいつの日か御楯とゆかん君とちぎりて。けなげな心情で男を送った女達も半年の月日のうちに夫君の位牌にぬかずくことも事務的になるばかりであろうし、やがて新たな面影を胸に宿すのも遠い日のことではない。人間が変ったのではない。人間は元来そういうものであり、変ったのは世相の上皮だけのことだ。
 　昔、四十七士の助命を排して処刑を断行した理由の一つは、彼等が生きながらえて生き恥をさらし折角の名を汚す者が現れてはいけないという老婆心であったそうな。現代の法律にこんな人情は存在しない。けれども人の心情には多分にこの傾向が残っており、美しいものを美しいままで終らせたいということは一般的な心情の一つのようだ。十数年前だかに童貞処女のまま愛の一生を終らせようと大磯のどこかで心中した学生と娘があったが世人の同情は大きかったし、私自身も、数年前に私と極めて親しかった姪の一人が二十一の年に自殺したとき、美しいうちに死んでくれて良かったような気がした。</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/001095/./files/42620_21407.html</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="80" customHeight="1">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>堕落論</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>坂口安吾</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>現に私自身が自分に課した文学の道とはかかる曠野の流浪であるが、それにも拘らず美しいものを美しいままで終らせたいという小さな希いを消し去るわけにも行かぬ。未完の美は美ではない。その当然堕ちるべき地獄での遍歴に淪落自体が美でありうる時に始めて美とよびうるのかも知れないが、二十の処女をわざわざ六十の老醜の姿の上で常に見つめなければならぬのか。これは私には分らない。私は二十の美女を好む。
+　死んでしまえば身も蓋もないというが、果してどういうものであろうか。敗戦して、結局気の毒なのは戦歿した英霊達だ、という考え方も私は素直に肯定することができない。けれども、六十すぎた将軍達が尚生に恋々として法廷にひかれることを思うと、何が人生の魅力であるか、私には皆目分らず、然し恐らく私自身も、もしも私が六十の将軍であったなら矢張り生に恋々として法廷にひかれるであろうと想像せざるを得ないので、私は生という奇怪な力にただ茫然たるばかりである。私は二十の美女を好むが、老将軍も亦二十の美女を好んでいるのか。そして戦歿の英霊が気の毒なのも二十の美女を好む意味に於てであるか。そのように姿の明確なものなら、</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/001095/./files/42620_21407.html</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>斜陽</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>太宰治</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>一
 　朝、食堂でスウプを一さじ、すっと吸ってお母さまが、
@@ -1165,32 +2049,85 @@
 「爵位があるから、貴族だというわけにはいかないんだぜ。爵位が無くても、天爵というものを持っている立派な貴族のひともあるし、おれたちのように爵位だけは持っていても、貴族どころか、賤民にちかいのもいる。岩島なんてのは（と直治の学友の伯爵のお名前を挙げて）あんなのは、まったく、新宿の遊廓の客引き番頭よりも、もっとげびてる感じじゃねえか。こないだも、柳井（と、</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000035/./files/1565_8559.html</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="80" customHeight="1">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>斜陽</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>太宰治</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>帰りましょう。おそくなると、困るんでしょう？」
+「いいえ、かまわないんですの」
+「いや、実は、こっちが窮屈でいけねえんだ。ねえさん！　会計！」
+「うんと高いのでしょうか。少しなら、私、持っているんですけど」
+「そう。そんなら、会計は、あなただ」
+「足りないかも知れませんわ」
+　私は、バッグの中を見て、お金がいくらあるかを上原さんに教えた。
+「それだけあれば、もう二、三軒飲める。馬鹿にしてやがる」
+　上原さんは顔をしかめておっしゃって、それから笑った。
+「どこかへ、また、飲みにおいでになりますか？」
+　と、おたずねしたら、まじめに首を振って、
+「いや、もうたくさん。タキシーを拾ってあげますから、お帰りなさい」
+　私たちは、地下室の暗い階段をのぼって行った。一歩さきにのぼって行く上原さんが、階段の中頃で、くるりとこちら向きになり、素早く私にキスをした。私は唇を固く閉じたまま、それを受けた。
+　べつに何も、上原さんをすきでなかったのに、それでも、その時から私に、あの「ひめごと」が出来てしまったのだ。かたかたかたと、上原さんは走って階段を上って行って、私は不思議な透明な気分で、ゆっくり上って、</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000035/./files/1565_8559.html</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="80" customHeight="1">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>人間失格</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>太宰治</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>はしがき
 　私は、その男の写真を三葉、見たことがある。
@@ -1202,32 +2139,76 @@
 　まったく、その子供の笑顔は、よく見れば見るほど、何とも知れず、イヤな薄気味悪いものが感ぜられて来る。どだい、それは、笑顔でない。この子は、</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000035/./files/301_14912.html</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="80" customHeight="1">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="80" customHeight="1">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>人間失格</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>太宰治</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>もともと、非合法の興味だけから、そのグルウプの手伝いをしていたのですし、こんなに、それこそ冗談から駒が出たように、いやにいそがしくなって来ると、自分は、ひそかにＰのひとたちに、それはお門ちがいでしょう、あなたたちの直系のものたちにやらせたらどうですか、というようないまいましい感を抱くのを禁ずる事が出来ず、逃げました。逃げて、さすがに、いい気持はせず、死ぬ事にしました。
+　その頃、自分に特別の好意を寄せている女が、三人いました。ひとりは、自分の下宿している仙遊館の娘でした。この娘は、自分がれいの運動の手伝いでへとへとになって帰り、ごはんも食べずに寝てしまってから、必ず用箋と万年筆を持って自分の部屋にやって来て、
+「ごめんなさい。下では、妹や弟がうるさくて、ゆっくり手紙も書けないのです」
+　と言って、何やら自分の机に向って一時間以上も書いているのです。
+　自分もまた、知らん振りをして寝ておればいいのに、いかにもその娘が何か自分に言ってもらいたげの様子なので、れいの受け身の奉仕の精神を発揮して、実に一言も口をききたくない気持なのだけれども、くたくたに疲れ切っているからだに、</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000035/./files/301_14912.html</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>途中</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="80" customHeight="1">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>ごん狐</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>新美南吉</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>一
 　これは、私が小さいときに、村の茂平というおじいさんからきいたお話です。
@@ -1238,9 +2219,62 @@
 　ごんは、村の小川の堤まで出て来ました。あたりの、すすきの穂には、まだ雨のしずくが光っていました。川は、いつもは水が少いのですが、三日もの雨で、水が、どっとましていました。</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://www.aozora.gr.jp/cards/000121/./files/628_14895.html</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>冒頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ごん狐</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>新美南吉</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>かわいそうに兵十は、いわし屋にぶんなぐられて、あんな傷までつけられたのか。
+　ごんはこうおもいながら、そっと物置の方へまわってその入口に、栗をおいてかえりました。
+　つぎの日も、そのつぎの日もごんは、栗をひろっては、兵十の家へもって来てやりました。そのつぎの日には、栗ばかりでなく、まつたけも二、三ぼんもっていきました。
+四
+　月のいい晩でした。ごんは、ぶらぶらあそびに出かけました。中山さまのお城の下を通ってすこしいくと、細い道の向うから、だれか来るようです。話声が聞えます。チンチロリン、チンチロリンと松虫が鳴いています。
+　ごんは、道の片がわにかくれて、じっとしていました。話声はだんだん近くなりました。それは、兵十と加助というお百姓でした。
+「そうそう、なあ加助」と、兵十がいいました。
+「ああん？」
+「おれあ、このごろ、とてもふしぎなことがあるんだ」
+「何が？」
+「おっ母が死んでからは、だれだか知らんが、おれに栗やまつたけなんかを、まいにちまいにちくれるんだよ」
+「ふうん、だれが？」
+「それがわからんのだよ。おれの知らんうちに、おいていくんだ」
+　ごんは、</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.aozora.gr.jp/cards/000121/./files/628_14895.html</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>途中</t>
         </is>
       </c>
     </row>

--- a/aozora-quiz/questions-data.xlsx
+++ b/aozora-quiz/questions-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toukyoushi/Desktop/栞のたより/HP/aozora-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBA8A1F-220B-7843-AD39-4AA8BEC47CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C0E5CB-71BA-AF4A-A310-2706B41DE978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -52,6 +52,10 @@
     <t>easy</t>
   </si>
   <si>
+    <t>　私はその人を常に先生と呼んでいた。だからここでもただ先生と書くだけで本名は打ち明けない。これは世間を憚かる遠慮というよりも、その方が私にとって自然だからである。私はその人の記憶を呼び起すごとに、すぐ「先生」といいたくなる。筆を執っても心持は同じ事である。よそよそしい頭文字などはとても使う気にならない。
+　私が先生と知り合いになったのは鎌倉である。その時私はまだ若々しい書生であった。暑中休暇を利用して海水浴に行った友達からぜひ来いという端書を受け取ったので、私は多少の金を工面して、出掛ける事にした。私は金の工面に二、三日を費やした。ところが私が鎌倉に着いて三日と経たないうちに、私を呼び寄せた友達は、急に国元から帰れという電報を受け取った。電報には母が病気だからと断ってあったけれども友達はそれを信じなかった。友達はかねてから国元にいる親たちに勧まない結婚を強いられていた。彼は現代の習慣からいうと結婚するにはあまり年が若過ぎた。それに肝心の当人が気に入らなかった。それで夏休みに当然帰るべきところを、わざと避けて東京の近くで遊んでいたのである。</t>
+  </si>
+  <si>
     <t>https://www.aozora.gr.jp/cards/000148/./files/773_14560.html</t>
   </si>
   <si>
@@ -61,10 +65,23 @@
     <t>medium</t>
   </si>
   <si>
+    <t>しかしおれの方から見てご覧、立場が少し違っているよ。つまり卒業はお前に取ってより、このおれに取って結構なんだ。解ったかい」
+　私は一言もなかった。詫まる以上に恐縮して俯向いていた。父は平気なうちに自分の死を覚悟していたものとみえる。しかも私の卒業する前に死ぬだろうと思い定めていたとみえる。その卒業が父の心にどのくらい響くかも考えずにいた私は全く愚かものであった。私は鞄の中から卒業証書を取り出して、それを大事そうに父と母に見せた。証書は何かに圧し潰されて、元の形を失っていた。父はそれを鄭寧に伸した。
+「こんなものは巻いたなり手に持って来るものだ」
+「中に心でも入れると好かったのに」と母も傍から注意した。
+　父はしばらくそれを眺めた後、起って床の間の所へ行って、誰の目にもすぐはいるような正面へ証書を置いた。いつもの私ならすぐ何とかいうはずであったが、その時の私はまるで平生と違っていた。父や母に対して少しも逆らう気が起らなかった。私はだまって父の為すがままに任せておいた。一旦癖のついた鳥の子紙の証書は、なかなか父の自由にならなかった。適当な位置に置かれるや否や、</t>
+  </si>
+  <si>
     <t>途中</t>
   </si>
   <si>
     <t>坊っちゃん</t>
+  </si>
+  <si>
+    <t>一
+　親譲りの無鉄砲で小供の時から損ばかりしている。小学校に居る時分学校の二階から飛び降りて一週間ほど腰を抜かした事がある。なぜそんな無闇をしたと聞く人があるかも知れぬ。別段深い理由でもない。新築の二階から首を出していたら、同級生の一人が冗談に、いくら威張っても、そこから飛び降りる事は出来まい。弱虫やーい。と囃したからである。小使に負ぶさって帰って来た時、おやじが大きな眼をして二階ぐらいから飛び降りて腰を抜かす奴があるかと云ったから、この次は抜かさずに飛んで見せますと答えた。
+　親類のものから西洋製のナイフを貰って奇麗な刃を日に翳して、友達に見せていたら、一人が光る事は光るが切れそうもないと云った。切れぬ事があるか、何でも切ってみせると受け合った。そんなら君の指を切ってみろと注文したから、何だ指ぐらいこの通りだと右の手の親指の甲をはすに切り込んだ。幸ナイフが小さいのと、親指の骨が堅かったので、今だに親指は手に付いている。しかし創痕は死ぬまで消えぬ。
+　庭を東へ二十歩に行き尽すと、南上がりにいささかばかりの菜園があって、真中に栗の木が一本立っている。これは命より大事な栗だ。</t>
   </si>
   <si>
     <t>https://www.aozora.gr.jp/cards/000148/./files/752_14964.html</t>
@@ -530,26 +547,6 @@
 「ふうん、だれが？」
 「それがわからんのだよ。おれの知らんうちに、おいていくんだ」
 　ごんは、</t>
-  </si>
-  <si>
-    <t>　私はその人を常に先生と呼んでいた。だからここでもただ先生と書くだけで本名は打ち明けない。これは世間を憚かる遠慮というよりも、その方が私にとって自然だからである。私はその人の記憶を呼び起すごとに、すぐ「先生」といいたくなる。筆を執っても心持は同じ事である。よそよそしい頭文字などはとても使う気にならない。
-　私が先生と知り合いになったのは鎌倉である。その時私はまだ若々しい書生であった。暑中休暇を利用して海水浴に行った友達からぜひ来いという端書を受け取ったので、私は多少の金を工面して、出掛ける事にした。私は金の工面に二、三日を費やした。ところが私が鎌倉に着いて三日と経たないうちに、私を呼び寄せた友達は、急に国元から帰れという電報を受け取った。電報には母が病気だからと断ってあったけれども友達はそれを信じなかった。友達はかねてから国元にいる親たちに勧まない結婚を強いられていた。彼は現代の習慣からいうと結婚するにはあまり年が若過ぎた。それに肝心の当人が気に入らなかった。それで夏休みに当然帰るべきところを、わざと避けて東京の近くで遊んでいたのである。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>しかしおれの方から見てご覧、立場が少し違っているよ。つまり卒業はお前に取ってより、このおれに取って結構なんだ。解ったかい」
-　私は一言もなかった。詫まる以上に恐縮して俯向いていた。父は平気なうちに自分の死を覚悟していたものとみえる。しかも私の卒業する前に死ぬだろうと思い定めていたとみえる。その卒業が父の心にどのくらい響くかも考えずにいた私は全く愚かものであった。私は鞄の中から卒業証書を取り出して、それを大事そうに父と母に見せた。証書は何かに圧し潰されて、元の形を失っていた。父はそれを鄭寧に伸した。
-「こんなものは巻いたなり手に持って来るものだ」
-「中に心でも入れると好かったのに」と母も傍から注意した。
-　父はしばらくそれを眺めた後、起って床の間の所へ行って、誰の目にもすぐはいるような正面へ証書を置いた。いつもの私ならすぐ何とかいうはずであったが、その時の私はまるで平生と違っていた。父や母に対して少しも逆らう気が起らなかった。私はだまって父の為すがままに任せておいた。一旦癖のついた鳥の子紙の証書は、なかなか父の自由にならなかった。適当な位置に置かれるや否や、</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一
-　親譲りの無鉄砲で小供の時から損ばかりしている。小学校に居る時分学校の二階から飛び降りて一週間ほど腰を抜かした事がある。なぜそんな無闇をしたと聞く人があるかも知れぬ。別段深い理由でもない。新築の二階から首を出していたら、同級生の一人が冗談に、いくら威張っても、そこから飛び降りる事は出来まい。弱虫やーい。と囃したからである。小使に負ぶさって帰って来た時、おやじが大きな眼をして二階ぐらいから飛び降りて腰を抜かす奴があるかと云ったから、この次は抜かさずに飛んで見せますと答えた。
-　親類のものから西洋製のナイフを貰って奇麗な刃を日に翳して、友達に見せていたら、一人が光る事は光るが切れそうもないと云った。切れぬ事があるか、何でも切ってみせると受け合った。そんなら君の指を切ってみろと注文したから、何だ指ぐらいこの通りだと右の手の親指の甲をはすに切り込んだ。幸ナイフが小さいのと、親指の骨が堅かったので、今だに親指は手に付いている。しかし創痕は死ぬまで消えぬ。
-　庭を東へ二十歩に行き尽すと、南上がりにいささかばかりの菜園があって、真中に栗の木が一本立っている。これは命より大事な栗だ。</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -606,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -614,11 +611,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -964,13 +995,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="80" customHeight="1">
@@ -984,16 +1015,16 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="80" customHeight="1">
@@ -1001,7 +1032,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1010,13 +1041,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="80" customHeight="1">
@@ -1024,22 +1055,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="80" customHeight="1">
@@ -1047,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -1056,13 +1087,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="80" customHeight="1">
@@ -1070,22 +1101,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="80" customHeight="1">
@@ -1093,7 +1124,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -1102,13 +1133,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="80" customHeight="1">
@@ -1116,22 +1147,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="80" customHeight="1">
@@ -1139,22 +1170,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="80" customHeight="1">
@@ -1162,22 +1193,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="80" customHeight="1">
@@ -1185,22 +1216,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="80" customHeight="1">
@@ -1208,22 +1239,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="80" customHeight="1">
@@ -1231,22 +1262,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="80" customHeight="1">
@@ -1254,22 +1285,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="80" customHeight="1">
@@ -1277,22 +1308,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="80" customHeight="1">
@@ -1300,22 +1331,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="80" customHeight="1">
@@ -1323,22 +1354,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="80" customHeight="1">
@@ -1346,22 +1377,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="80" customHeight="1">
@@ -1369,22 +1400,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="80" customHeight="1">
@@ -1392,22 +1423,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="80" customHeight="1">
@@ -1415,22 +1446,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="80" customHeight="1">
@@ -1438,22 +1469,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="80" customHeight="1">
@@ -1461,22 +1492,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="80" customHeight="1">
@@ -1484,22 +1515,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="80" customHeight="1">
@@ -1507,22 +1538,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="80" customHeight="1">
@@ -1530,22 +1561,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="80" customHeight="1">
@@ -1553,22 +1584,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="80" customHeight="1">
@@ -1576,22 +1607,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="80" customHeight="1">
@@ -1599,22 +1630,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="80" customHeight="1">
@@ -1622,22 +1653,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="80" customHeight="1">
@@ -1645,22 +1676,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="80" customHeight="1">
@@ -1668,22 +1699,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="80" customHeight="1">
@@ -1691,22 +1722,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="80" customHeight="1">
@@ -1714,22 +1745,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F35" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="80" customHeight="1">
@@ -1737,22 +1768,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="80" customHeight="1">
@@ -1760,22 +1791,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="80" customHeight="1">
@@ -1783,22 +1814,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="80" customHeight="1">
@@ -1806,22 +1837,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="80" customHeight="1">
@@ -1829,22 +1860,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="80" customHeight="1">
@@ -1852,22 +1883,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="80" customHeight="1">
@@ -1875,22 +1906,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="80" customHeight="1">
@@ -1898,22 +1929,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G43" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="80" customHeight="1">
@@ -1921,22 +1952,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="80" customHeight="1">
@@ -1944,22 +1975,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F45" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G45" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="80" customHeight="1">
@@ -1967,22 +1998,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F46" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="80" customHeight="1">
@@ -1990,28 +2021,26 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>109</v>
+        <v>67</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="F47" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="356">
-      <c r="E48" s="2" t="s">
-        <v>109</v>
-      </c>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="356" customHeight="1">
+      <c r="E48" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
